--- a/site/exports/bnu-psychology.xlsx
+++ b/site/exports/bnu-psychology.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,118 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>心理学部</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Purposeful partial professional biography, not comprehensive school coverage.；Degree conferral and award dates unknown; doctoral title not used as conferral evidence. Own advisors unknown.；Work/visit roles and nondegree postdoctoral events distinguished.；Current employment unverified; institutional labels preserved rather than silently renamed.；Selected bibliography from official page only; publisher/full text not verified.；Necessary original professional tool-output lines retained privately; raw page-title identity included, contact-bearing header omitted; no clinical guidance.；来源工作单位：心理学院（原文工作单位）。本站归入“心理学部”仅供展示分类，不据此认定机构更名、同一组织或当前任职；原单位名称保留。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>心理学部</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Purposeful partial professional biography, not comprehensive school coverage.；Degree conferral and award dates unknown; doctoral title not used as conferral evidence. Own advisors unknown.；Work/visit roles and nondegree postdoctoral events distinguished.；Current employment unverified; institutional labels preserved rather than silently renamed.；Selected bibliography from official page only; publisher/full text not verified.；Necessary original professional tool-output lines retained privately; raw page-title identity included, contact-bearing header omitted; no clinical guidance.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,13 +692,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="29.4" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="29.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -601,7 +709,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="49" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
@@ -666,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1030,14 +1138,590 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学心理系</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>应用心理学</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学心理学院</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>心理测量与评价</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学心理学院</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>心理测量与评价</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学心理学院</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：教授；来源institution_as_source：北京师范大学心理学院；来源period_as_source：2020-至今</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>访问学者</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>英国剑桥大学心理系</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：访问学者；来源institution_as_source：英国剑桥大学心理系；来源period_as_source：2015.9-2016.9</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>中国科学技术大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>生物学</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>理学博士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>中国科学院研究生院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>生物物理</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>postdoctoral_research</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>中科院生物物理所脑与认知科学国家重点实验室</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学心理学部</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：教授；来源institution_as_source：北京师范大学心理学部；来源period_as_source：2018-至今</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S6"/>
+  <autoFilter ref="A1:S15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1140,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1331,8 +2015,164 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>应用心理统计学</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>coauthored_book</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：刘红云、骆方；来源person_contribution_role_as_source：coauthor, explicitly 著</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SPSS数据统计与分析</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>coauthored_book</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：骆方、刘红云、黄崑；来源person_contribution_role_as_source：coauthor, explicitly 著</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Temporal dynamics of quantity processing: distinct time course and representational patterns revealed by multivariate pattern analysis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Tian J, Xu W, Si B, Sun G*, &amp; Zhou K*；来源person_contribution_role_as_source：listed author; asterisk not defined in retained lines, no corresponding-author inference；来源书目信息（卷）：318；来源书目信息（文章编号）：121367</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1340,6 +2180,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1351,14 +2197,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="19.6" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1466,11 +2312,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>骆方</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-luofang-psychology-s001-39a3f8d91c26</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/lf/index.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:46:27Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>周可</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-bnu-zhouke-psychology-s001-ab42c4504c60</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://psych.bnu.edu.cn/szdw/zrjs/js/zk/index.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:46:36Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>bnu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/bnu-psychology.xlsx
+++ b/site/exports/bnu-psychology.xlsx
@@ -1492,7 +1492,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
